--- a/stories/arbres/TREE-SAN-032.xlsx
+++ b/stories/arbres/TREE-SAN-032.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Adam est avec maman, au bord de la mer. Adam a envie de jouer. maman est là, tout près. On va apprendre : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam écoute maman. Adam entend les mots : goûter, petite portion, nommer le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la cuisine. Un chat miaule une fois. maman sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On écoute jusqu'au bout. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers la cuisine. Un chat miaule une fois. maman sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers la cuisine. Un chat miaule une fois. maman sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On écoute jusqu'au bout.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam respire. Adam retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2401,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2596,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2705,6 +2763,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2930,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3097,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3264,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3431,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3598,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3765,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3960,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4029,6 +4127,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4294,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4461,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4628,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4677,6 +4795,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4962,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5129,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5191,6 +5324,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5353,6 +5491,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5658,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5825,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5992,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6159,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6326,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6187,7 +6355,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers le jardin. Les chaussures font toc toc. maman sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers le jardin. Les chaussures font toc toc. maman sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6325,6 +6493,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers le jardin. Les chaussures font toc toc. maman sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6679,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6852,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam respire. Adam retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7047,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7025,6 +7214,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7409,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7377,6 +7576,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7743,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7910,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8077,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8244,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8411,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8578,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8539,6 +8773,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8701,6 +8940,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9107,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9274,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9441,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9608,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9775,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9942,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10137,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10025,6 +10304,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10471,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10638,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10805,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10972,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11139,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10859,7 +11168,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Adam va vers la chambre. La couverture est douce. maman sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Adam va vers la chambre. La couverture est douce. maman sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10997,6 +11306,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Adam va vers la chambre. La couverture est douce. maman sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Adam se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam respire. Adam retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11860,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12027,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On rit un peu. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11887,6 +12222,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12049,6 +12389,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12556,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12723,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12890,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13057,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13224,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13391,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13211,6 +13586,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13373,6 +13753,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13920,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14087,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14254,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14021,6 +14421,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14588,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14345,6 +14755,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14535,6 +14950,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14697,6 +15117,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15284,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15451,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15618,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15785,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Adam rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15952,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15542,6 +15992,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-032.xlsx
+++ b/stories/arbres/TREE-SAN-032.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Adam est avec maman, au bord de la mer. Adam a envie de jouer. maman est là, tout près. On va apprendre : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam écoute maman. Adam entend les mots : goûter, petite portion, nommer le goût.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam respire. Adam retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2406,6 +2417,7 @@
           <t>narrateur|Adam a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2768,6 +2781,7 @@
           <t>narrateur|Adam rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2935,6 +2949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3102,6 +3117,7 @@
           <t>narrateur|Adam rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3269,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3436,6 +3453,7 @@
           <t>narrateur|Adam rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3603,6 +3621,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3789,7 @@
           <t>narrateur|Adam a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3965,6 +3985,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4132,6 +4153,7 @@
           <t>narrateur|Adam rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4299,6 +4321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4466,6 +4489,7 @@
           <t>narrateur|Adam rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4633,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4800,6 +4825,7 @@
           <t>narrateur|Adam rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4967,6 +4993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5134,6 +5161,7 @@
           <t>narrateur|Adam a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5329,6 +5357,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5496,6 +5525,7 @@
           <t>narrateur|Adam rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5663,6 +5693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5830,6 +5861,7 @@
           <t>narrateur|Adam rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5997,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6164,6 +6197,7 @@
           <t>narrateur|Adam rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6331,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6534,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6722,7 @@
           <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6857,6 +6894,7 @@
           <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam respire. Adam retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7052,6 +7090,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
           <t>narrateur|Adam a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
           <t>narrateur|Adam rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>narrateur|Adam rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>narrateur|Adam rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Adam a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>narrateur|Adam rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>narrateur|Adam rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9613,6 +9666,7 @@
           <t>narrateur|Adam rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9780,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9947,6 +10002,7 @@
           <t>narrateur|Adam a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10142,6 +10198,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10309,6 +10366,7 @@
           <t>narrateur|Adam rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10476,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10643,6 +10702,7 @@
           <t>narrateur|Adam rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10810,6 +10870,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10977,6 +11038,7 @@
           <t>narrateur|Adam rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11144,6 +11206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam respire. Adam retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12099,7 @@
           <t>narrateur|Adam a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On rit un peu. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12227,6 +12295,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12394,6 +12463,7 @@
           <t>narrateur|Adam rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12799,7 @@
           <t>narrateur|Adam rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13135,7 @@
           <t>narrateur|Adam rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13471,7 @@
           <t>narrateur|Adam a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13591,6 +13667,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13758,6 +13835,7 @@
           <t>narrateur|Adam rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13925,6 +14003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14092,6 +14171,7 @@
           <t>narrateur|Adam rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14259,6 +14339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14426,6 +14507,7 @@
           <t>narrateur|Adam rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14593,6 +14675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14760,6 +14843,7 @@
           <t>narrateur|Adam a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14955,6 +15039,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15122,6 +15207,7 @@
           <t>narrateur|Adam rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le matin. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15289,6 +15375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15456,6 +15543,7 @@
           <t>narrateur|Adam rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et après la sieste. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15623,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15790,6 +15879,7 @@
           <t>narrateur|Adam rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et le soir. Adam a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Adam a entendu : goûter, petite portion, nommer le goût. Adam dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15957,6 +16047,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15975,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15999,6 +16090,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16200,6 +16305,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
